--- a/estadistica2/data/aravena_caro.xlsx
+++ b/estadistica2/data/aravena_caro.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kennethbunker/Library/CloudStorage/Dropbox/GitHub/uss/estadistica2/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDBB9284-E450-4743-8C85-8E1AB3132280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF4EEBED-E991-F342-8114-0222E3058AF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15720" xr2:uid="{BFB33887-8355-4972-897E-6059AD8D8853}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15720" activeTab="2" xr2:uid="{BFB33887-8355-4972-897E-6059AD8D8853}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
     <sheet name="codebook" sheetId="2" r:id="rId2"/>
-    <sheet name="Hoja3" sheetId="3" r:id="rId3"/>
+    <sheet name="variables" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">data!$A$1:$I$1</definedName>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2360" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2366" uniqueCount="223">
   <si>
     <t>Variable Dependiente</t>
   </si>
@@ -691,12 +691,30 @@
   <si>
     <t>variable</t>
   </si>
+  <si>
+    <t>descripcion</t>
+  </si>
+  <si>
+    <t>medicion</t>
+  </si>
+  <si>
+    <t>Variable Independiente 1</t>
+  </si>
+  <si>
+    <t>Variable Independiente 2</t>
+  </si>
+  <si>
+    <t>Variable Independiente 3</t>
+  </si>
+  <si>
+    <t>Variable Independiente 4</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -708,6 +726,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -751,7 +775,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -778,15 +802,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -24534,73 +24549,97 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4866322-3984-4E0F-88A1-DCB4132E82E7}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.1640625" customWidth="1"/>
+    <col min="1" max="3" width="15.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="9" t="s">
         <v>216</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2">
         <v>1990</v>
       </c>
-      <c r="C2">
+      <c r="E2">
         <v>2023</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="11" t="s">
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="6" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="8" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="8" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="12" t="s">
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="8" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="12" t="s">
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="8" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="12" t="s">
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="8" t="s">
         <v>211</v>
       </c>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -24609,7 +24648,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72660A5D-9B0D-4073-9AFD-E893863F6E00}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
@@ -24624,7 +24663,28 @@
         <v>1</v>
       </c>
     </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>222</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/estadistica2/data/aravena_caro.xlsx
+++ b/estadistica2/data/aravena_caro.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kennethbunker/Library/CloudStorage/Dropbox/GitHub/uss/estadistica2/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF4EEBED-E991-F342-8114-0222E3058AF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA90C927-5AD6-9B41-9508-D212553F97AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15720" activeTab="2" xr2:uid="{BFB33887-8355-4972-897E-6059AD8D8853}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15720" xr2:uid="{BFB33887-8355-4972-897E-6059AD8D8853}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="variables" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">data!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$I$780</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2366" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2394" uniqueCount="246">
   <si>
     <t>Variable Dependiente</t>
   </si>
@@ -692,9 +692,6 @@
     <t>variable</t>
   </si>
   <si>
-    <t>descripcion</t>
-  </si>
-  <si>
     <t>medicion</t>
   </si>
   <si>
@@ -708,6 +705,78 @@
   </si>
   <si>
     <t>Variable Independiente 4</t>
+  </si>
+  <si>
+    <t>año de la eleccion</t>
+  </si>
+  <si>
+    <t>nombre del partido politico del candidato</t>
+  </si>
+  <si>
+    <t>9.0</t>
+  </si>
+  <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>3,476,333</t>
+  </si>
+  <si>
+    <t>tipo de cargo al que postulo</t>
+  </si>
+  <si>
+    <t>Variable Independiente 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">independiente </t>
+  </si>
+  <si>
+    <t>voto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tipo 2 </t>
+  </si>
+  <si>
+    <t>Variable Independiente 6</t>
+  </si>
+  <si>
+    <t>Variable Independiente 7</t>
+  </si>
+  <si>
+    <t>Variable Independiente 8</t>
+  </si>
+  <si>
+    <t>orientacion politica del partido</t>
+  </si>
+  <si>
+    <t>puntaje ideologico del partido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El candidato es idependiente </t>
+  </si>
+  <si>
+    <t>numero de votos obtenidos</t>
+  </si>
+  <si>
+    <t>numero de elecciones</t>
+  </si>
+  <si>
+    <t>alcalde</t>
+  </si>
+  <si>
+    <t>senador</t>
+  </si>
+  <si>
+    <t>centro</t>
+  </si>
+  <si>
+    <t>derecho</t>
+  </si>
+  <si>
+    <t>a pulso, por el buen vivir</t>
+  </si>
+  <si>
+    <t>yo marco por el cambio</t>
   </si>
 </sst>
 </file>
@@ -737,7 +806,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -762,6 +831,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -775,7 +850,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -801,7 +876,39 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -24537,7 +24644,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1" xr:uid="{499110A3-C7DE-4DCB-8161-8B8FED30AFB7}">
+  <autoFilter ref="A1:I780" xr:uid="{499110A3-C7DE-4DCB-8161-8B8FED30AFB7}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I780">
       <sortCondition ref="H1:H780"/>
     </sortState>
@@ -24549,97 +24656,146 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4866322-3984-4E0F-88A1-DCB4132E82E7}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="15.1640625" customWidth="1"/>
+    <col min="1" max="1" width="15.1640625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="28.83203125" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="11.5" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="9" t="s">
         <v>216</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="D1" s="9" t="s">
+      <c r="C1" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="D1" s="14" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2">
+      <c r="B2" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="C2" s="18">
         <v>1990</v>
       </c>
-      <c r="E2">
+      <c r="D2" s="18">
         <v>2023</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+      <c r="A3" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+      <c r="B3" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>244</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
+      <c r="B4" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="8" t="s">
+      <c r="B5" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="8" t="s">
+      <c r="B6" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="C6" s="18">
+        <v>0</v>
+      </c>
+      <c r="D6" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="8" t="s">
+      <c r="B7" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="C7" s="18">
+        <v>108</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="8" t="s">
+      <c r="B8" s="17"/>
+      <c r="D8" s="19"/>
+    </row>
+    <row r="9" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="8" t="s">
+      <c r="B9" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
+      <c r="B10" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="C10" s="18">
+        <v>0</v>
+      </c>
+      <c r="D10" s="18">
+        <v>34</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -24648,39 +24804,83 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72660A5D-9B0D-4073-9AFD-E893863F6E00}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>219</v>
+        <v>218</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>220</v>
+        <v>219</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>221</v>
+        <v>220</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>222</v>
+        <v>221</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>232</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>233</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>234</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>211</v>
       </c>
     </row>
   </sheetData>
